--- a/Master/9387r00/9387r00 @ 0.208 IPR_cutlet_data.xlsx
+++ b/Master/9387r00/9387r00 @ 0.208 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>1.235</v>
+        <v>1.241</v>
       </c>
       <c r="B34" s="6" t="n">
         <v>1</v>
@@ -1126,7 +1126,7 @@
         <v>3.4221</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>-1.7193</v>
+        <v>-2.3968</v>
       </c>
       <c r="F34" s="7" t="n">
         <v>0.0004</v>
@@ -1134,7 +1134,7 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>2.234</v>
+        <v>2.24</v>
       </c>
       <c r="B35" s="6" t="n">
         <v>2</v>
@@ -1146,7 +1146,7 @@
         <v>3.4221</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-1.5707</v>
+        <v>-2.2482</v>
       </c>
       <c r="F35" s="7" t="n">
         <v>0.0004</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>1.223</v>
+        <v>1.235</v>
       </c>
       <c r="B36" s="6" t="n">
         <v>1</v>
@@ -1163,98 +1163,98 @@
         <v>2</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>3.482</v>
+        <v>3.4221</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>-0.2176</v>
+        <v>-1.7193</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>0.0012</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>1.123</v>
+        <v>2.234</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>3.5001</v>
+        <v>3.4221</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-0.2039</v>
+        <v>-1.5707</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>0.0026</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>6.124</v>
+        <v>1.223</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>3.5708</v>
+        <v>3.482</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>-0.1789</v>
+        <v>-0.2176</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>0.0303</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>5.225</v>
+        <v>1.123</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>3.6295</v>
+        <v>3.5001</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>-0.32</v>
+        <v>-0.2039</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0.0175</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>5.125</v>
+        <v>6.124</v>
       </c>
       <c r="B40" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>3.6752</v>
+        <v>3.5708</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>-0.3171</v>
+        <v>-0.1789</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>0.0086</v>
+        <v>0.0303</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>5.231</v>
+        <v>5.225</v>
       </c>
       <c r="B41" s="6" t="n">
         <v>5</v>
@@ -1263,213 +1263,253 @@
         <v>2</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>3.6826</v>
+        <v>3.6295</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-1.0749</v>
+        <v>-0.32</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>0.0004</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>4.126</v>
+        <v>5.125</v>
       </c>
       <c r="B42" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>3.7676</v>
+        <v>3.6752</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>-0.4984</v>
+        <v>-0.3171</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0.0123</v>
+        <v>0.0086</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>3.227</v>
+        <v>5.231</v>
       </c>
       <c r="B43" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C43" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>3.8152</v>
+        <v>3.6826</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-0.6665</v>
+        <v>-1.0749</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>0.0047</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>3.127</v>
+        <v>4.126</v>
       </c>
       <c r="B44" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>3.8274</v>
+        <v>3.7676</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>-0.6489</v>
+        <v>-0.4984</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>0.0058</v>
+        <v>0.0123</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>2.128</v>
+        <v>3.227</v>
       </c>
       <c r="B45" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>3.847</v>
+        <v>3.8152</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-0.756</v>
+        <v>-0.6665</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>0.0026</v>
+        <v>0.0047</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>6.23</v>
+        <v>3.127</v>
       </c>
       <c r="B46" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>3.8772</v>
+        <v>3.8274</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>-0.8769</v>
+        <v>-0.6489</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>0.0023</v>
+        <v>0.0058</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>1.229</v>
+        <v>2.128</v>
       </c>
       <c r="B47" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>3.8829</v>
+        <v>3.847</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>-0.9447</v>
+        <v>-0.756</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>0.0001</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>1.129</v>
+        <v>6.23</v>
       </c>
       <c r="B48" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>3.8959</v>
+        <v>3.8772</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>-0.9424</v>
+        <v>-0.8769</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.0024</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>6.13</v>
+        <v>1.229</v>
       </c>
       <c r="B49" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>3.8982</v>
+        <v>3.8829</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>-0.8783</v>
+        <v>-0.9447</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.0067</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>3.8959</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>-0.9424</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>0.0024</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>3.8982</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>-0.8783</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>0.0067</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n">
         <v>5.131</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B52" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C50" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="7" t="n">
+      <c r="C52" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="7" t="n">
         <v>3.9121</v>
       </c>
-      <c r="E50" s="7" t="n">
+      <c r="E52" s="7" t="n">
         <v>-1.0254</v>
       </c>
-      <c r="F50" s="7" t="n">
+      <c r="F52" s="7" t="n">
         <v>0.0037</v>
       </c>
     </row>
-    <row r="52">
-      <c r="E52" s="8" t="inlineStr">
+    <row r="54">
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F52" s="9" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="E53" s="8" t="inlineStr">
+      <c r="F54" s="9" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="E55" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F53" s="10" t="n">
-        <v>0.7868000000000001</v>
+      <c r="F55" s="10" t="n">
+        <v>0.7876</v>
       </c>
     </row>
   </sheetData>
